--- a/2026_段考詳解_網址總覽表.xlsx
+++ b/2026_段考詳解_網址總覽表.xlsx
@@ -1,249 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026_段考詳解\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F9A09AF-E270-40F0-8927-E94A51350AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{228EEE36-97F4-42E4-8258-258C77DF6339}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="段考詳解網址總覽" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="段考詳解網址總覽" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
-  <si>
-    <t>國中段考國文試題詳解（雙色螢光筆版）網址對照總覽表</t>
-  </si>
-  <si>
-    <t>製作者：臺北市立龍門國中 黃于珊、王斐亭老師 • 學思軒國文教室 • 線上發布平台：GitHub Pages</t>
-  </si>
-  <si>
-    <t>項次</t>
-  </si>
-  <si>
-    <t>學年度</t>
-  </si>
-  <si>
-    <t>年級學期</t>
-  </si>
-  <si>
-    <t>段考別</t>
-  </si>
-  <si>
-    <t>原始中文檔案名稱</t>
-  </si>
-  <si>
-    <t>英文標準檔案名稱</t>
-  </si>
-  <si>
-    <t>簡短跳轉檔名</t>
-  </si>
-  <si>
-    <t>總題數</t>
-  </si>
-  <si>
-    <t>題型單元涵蓋向度</t>
-  </si>
-  <si>
-    <t>GitHub Pages 線上直接瀏覽網址</t>
-  </si>
-  <si>
-    <t>教學特色與模式</t>
-  </si>
-  <si>
-    <t>總部入口</t>
-  </si>
-  <si>
-    <t>全站導覽</t>
-  </si>
-  <si>
-    <t>總目錄首頁</t>
-  </si>
-  <si>
-    <t>index.html (總目錄導覽首頁)</t>
-  </si>
-  <si>
-    <t>index.html</t>
-  </si>
-  <si>
-    <t>2 份大卷</t>
-  </si>
-  <si>
-    <t>完整收錄 114 七下段三、115 八上段一試卷卡片、關鍵字即時搜尋、左右開弓指南與 Excel 下載</t>
-  </si>
-  <si>
-    <t>https://oaoadna-1313.github.io/2026_exam_explanation/</t>
-  </si>
-  <si>
-    <t>全站總導覽首頁、即時關鍵字搜尋、年級分流標籤、一鍵複製網址、自適應響應式設計</t>
-  </si>
-  <si>
-    <t>114學年度</t>
-  </si>
-  <si>
-    <t>七年級下學期</t>
-  </si>
-  <si>
-    <t>第三次段考</t>
-  </si>
-  <si>
-    <t>114-2七下段三國文試題詳解雙色螢光筆版.html</t>
-  </si>
-  <si>
-    <t>exam-explanation-7-2-3.html</t>
-  </si>
-  <si>
-    <t>exam-7-2-3.html</t>
-  </si>
-  <si>
-    <t>57 題</t>
-  </si>
-  <si>
-    <t>國字注音 18 題、古詩默書 2 題、成語選擇 5 題、單題測驗 23 題、閱讀題組 3 大組 9 題</t>
-  </si>
-  <si>
-    <t>https://oaoadna-1313.github.io/2026_exam_explanation/exam-explanation-7-2-3.html</t>
-  </si>
-  <si>
-    <t>黃色螢光筆形式標記、綠色螢光筆破題攻擊、文言文全篇白話對譯、左右開弓學習、線上交卷計分</t>
-  </si>
-  <si>
-    <t>115學年度</t>
-  </si>
-  <si>
-    <t>八年級上學期</t>
-  </si>
-  <si>
-    <t>第一次段考</t>
-  </si>
-  <si>
-    <t>115-1八上段一國文試題詳解雙色螢光筆版.html</t>
-  </si>
-  <si>
-    <t>exam-explanation-8-1-1.html</t>
-  </si>
-  <si>
-    <t>exam-8-1-1.html</t>
-  </si>
-  <si>
-    <t>59 題</t>
-  </si>
-  <si>
-    <t>國字注音 20 題、田園之秋默書 1 題、成語選擇 5 題、單題測驗 23 題、閱讀題組 4 大組 10 題</t>
-  </si>
-  <si>
-    <t>https://oaoadna-1313.github.io/2026_exam_explanation/exam-explanation-8-1-1.html</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
-      <b/>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
-      <b/>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
-      <u/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="12"/>
-      <color theme="10"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FF1A24D0"/>
       <sz val="12"/>
-      <color rgb="FF1A24D0"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -310,77 +158,137 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -700,204 +608,273 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4BF026-F3F7-4331-8F95-4ACBF7A959D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.6328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.6328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col width="5.26953125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="10" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.36328125" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="10.36328125" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="42.26953125" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="28.1796875" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="16.453125" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="8.26953125" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
+    <col width="45.6328125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="75.7265625" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
+    <col width="45.6328125" customWidth="1" style="1" min="11" max="11"/>
+    <col width="8.7265625" customWidth="1" style="1" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+    <row r="1" ht="40" customHeight="1" s="16">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>國中段考國文試題詳解（雙色螢光筆版）網址對照總覽表</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="22" customHeight="1" s="16">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>製作者：臺北市立龍門國中 黃于珊、王斐亭老師 • 學思軒國文教室 • 線上發布平台：GitHub Pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="16">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>項次</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>學年度</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>年級學期</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>段考別</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>原始中文檔案名稱</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>英文標準檔案名稱</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>簡短跳轉檔名</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>總題數</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>題型單元涵蓋向度</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Pages 線上直接瀏覽網址</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>教學特色與模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" s="16">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>總部入口</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>全站導覽</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>總目錄首頁</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>index.html (總目錄導覽首頁)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>2 份大卷</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>完整收錄 114 七下段三、115 八上段一試卷卡片、關鍵字即時搜尋、左右開弓指南與 Excel 下載</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_exam_explanation/</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>全站總導覽首頁、即時關鍵字搜尋、年級分流標籤、一鍵複製網址、自適應響應式設計</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
+    <row r="5" ht="25" customHeight="1" s="16">
+      <c r="A5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>114學年度</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>七年級下學期</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>第三次段考</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>114-2七下段三國文試題詳解雙色螢光筆版.html</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>exam-explanation-7-2-3.html</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>exam-7-2-3.html</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>57 題</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>國字注音 18 題、古詩默書 2 題、成語選擇 5 題、單題測驗 23 題、閱讀題組 3 大組 9 題</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_exam_explanation/exam-explanation-7-2-3.html</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>黃色螢光筆形式標記、綠色螢光筆破題攻擊、文言文全篇白話對譯、左右開弓學習、線上交卷計分</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" s="16">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="10">
-        <v>2</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="13">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>31</v>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>115學年度</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>八年級上學期</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>第一次段考</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>115-1八上段一國文試題詳解雙色螢光筆版.html</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>exam-explanation-8-1-1.html</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>exam-8-1-1.html</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>國字注音 20 題、詩意配合 4 題、成語選擇 5 題、單題測驗 23 題、閱讀題組 4 大組 10 題</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_exam_explanation/exam-explanation-8-1-1.html</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>黃色螢光筆形式標記、綠色螢光筆破題攻擊、文言文全篇白話對譯、左右開弓學習、線上交卷計分</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" tooltip="點擊前往線上網頁" xr:uid="{42271761-1D13-4FE0-A3B7-1FB14110595E}"/>
-    <hyperlink ref="J5" r:id="rId2" tooltip="點擊前往線上網頁" xr:uid="{9FF3EE33-0810-4F1B-803D-34952C178624}"/>
-    <hyperlink ref="J6" r:id="rId3" tooltip="點擊前往線上網頁" xr:uid="{A188BBC1-42E1-43B2-9BA1-5C211F30533A}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" tooltip="點擊前往線上網頁" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" tooltip="點擊前往線上網頁" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" tooltip="點擊前往線上網頁" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
